--- a/artfynd/A 64590-2021 artfynd.xlsx
+++ b/artfynd/A 64590-2021 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 64590-2021 artfynd.xlsx
+++ b/artfynd/A 64590-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122481683</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 64590-2021 artfynd.xlsx
+++ b/artfynd/A 64590-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122481683</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64590-2021 artfynd.xlsx
+++ b/artfynd/A 64590-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122481683</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
